--- a/media/exports/reports/2026-07/growth-trades.xlsx
+++ b/media/exports/reports/2026-07/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>July's jobs made $71,121 gross margin (36.8%). Technician time not charged to jobs took ($2,214) and overheads $59,440, leaving $13,895 profit before tax (7.2% of revenue). To cover overheads, jobs need a 29.6% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>July's jobs made $93,486 gross margin (43.4%). Technician time not charged to jobs took $26,391 and overheads $59,440, leaving $7,655 profit before tax (3.6% of revenue). To cover overheads, jobs need a 39.8% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>$193,245 against $186,760</t>
+          <t>$215,610 against $208,588</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>$193,245 against $186,760</t>
+          <t>$215,610 against $208,588</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>$71,121 before overheads</t>
+          <t>$93,486 before overheads</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Revenue is 3.5% up on the same period last year, year to date ($193,245 against $186,760). Maintenance contracts make the highest gross margin (59.5%); Installations the lowest (28.3%). The business needs 29.6% gross margin just to cover overheads.</t>
+          <t>Revenue is 3.4% up on the same period last year, year to date ($215,610 against $208,588). Maintenance contracts make the highest gross margin (63.9%); Installations the lowest (36.0%). The business needs 39.8% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -963,10 +963,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Installations: 28.3% gross margin, 6.7 points under the 35.0% target: about $8,580 on $127,600 of revenue this financial year to date. It's below the 29.6% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 this financial year to date).</t>
+          <t>Installations: 36.0% gross margin, 1.0 points over the 35.0% target ($1,430 ahead on $143,000 this financial year to date). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>$40,500 against $33,200</t>
+          <t>$45,350 against $37,200</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>$40,500 against $33,200</t>
+          <t>$45,350 against $37,200</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>$24,116 before overheads</t>
+          <t>$28,966 before overheads</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts brought in $40,500 this financial year to date, 22.0% on the same period last year (faster than the business as a whole, 3.5%), at a 59.5% gross margin (above the 36.8% overall).</t>
+          <t>Maintenance contracts brought in $45,350 this financial year to date, 21.9% on the same period last year (faster than the business as a whole, 3.4%), at a 63.9% gross margin (above the 43.4% overall).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 this financial year to date).</t>
+          <t>Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>$127,600 against $135,800</t>
+          <t>$143,000 against $152,100</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>$127,600 against $135,800</t>
+          <t>$143,000 against $152,100</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>$36,080 before overheads</t>
+          <t>$51,480 before overheads</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Installations brought in $127,600 this financial year to date, (6.0%) on the same period last year (slower than the business as a whole, 3.5%), at a 28.3% gross margin (below the 36.8% overall).</t>
+          <t>Installations brought in $143,000 this financial year to date, (6.0%) on the same period last year (slower than the business as a whole, 3.4%), at a 36.0% gross margin (below the 43.4% overall).</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Installations: 28.3% gross margin, 6.7 points under the 35.0% target: about $8,580 on $127,600 of revenue this financial year to date. It's below the 29.6% needed to cover overheads, too.</t>
+          <t>Installations: 36.0% gross margin, 1.0 points over the 35.0% target ($1,430 ahead on $143,000 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>$25,145 against $17,760</t>
+          <t>$27,260 against $19,288</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>$25,145 against $17,760</t>
+          <t>$27,260 against $19,288</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>$10,925 before overheads</t>
+          <t>$13,040 before overheads</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs brought in $25,145 this financial year to date, 41.6% on the same period last year (faster than the business as a whole, 3.5%), at a 43.4% gross margin (above the 36.8% overall).</t>
+          <t>Call-outs and repairs brought in $27,260 this financial year to date, 41.3% on the same period last year (faster than the business as a whole, 3.4%), at a 47.8% gross margin (above the 43.4% overall).</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: 43.4% gross margin, 8.4 points over the 35.0% target ($2,124 ahead on $25,145 this financial year to date).</t>
+          <t>Call-outs and repairs: 47.8% gross margin, 12.8 points over the 35.0% target ($3,499 ahead on $27,260 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>71121</v>
+        <v>93486</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>54600</v>
+        <v>83205</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
     </row>
     <row r="16">
@@ -1506,7 +1506,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the July 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the July 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
     </row>
     <row r="26">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
     </row>
     <row r="27">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
     </row>
     <row r="34">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
     </row>
     <row r="35">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>71121</v>
+        <v>93486</v>
       </c>
     </row>
     <row r="37">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
     </row>
     <row r="44">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
     </row>
     <row r="45">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>71121</v>
+        <v>93486</v>
       </c>
     </row>
     <row r="47">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="54">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="55">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="62">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="63">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>24116</v>
+        <v>28966</v>
       </c>
     </row>
     <row r="65">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="72">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="73">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>24116</v>
+        <v>28966</v>
       </c>
     </row>
     <row r="75">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
     </row>
     <row r="82">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
     </row>
     <row r="83">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
     </row>
     <row r="90">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
     </row>
     <row r="91">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>36080</v>
+        <v>51480</v>
       </c>
     </row>
     <row r="93">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
     </row>
     <row r="100">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
     </row>
     <row r="101">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B102" s="12" t="n">
-        <v>36080</v>
+        <v>51480</v>
       </c>
     </row>
     <row r="103">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B109" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
     </row>
     <row r="110">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
     </row>
     <row r="111">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B117" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
     </row>
     <row r="118">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="B118" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
     </row>
     <row r="119">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="B120" s="12" t="n">
-        <v>10925</v>
+        <v>13040</v>
       </c>
     </row>
     <row r="121">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B127" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
     </row>
     <row r="128">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="B128" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
     </row>
     <row r="129">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B130" s="12" t="n">
-        <v>10925</v>
+        <v>13040</v>
       </c>
     </row>
     <row r="131">
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>114334</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>113016</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>85316</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>80742</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>102348</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>85752</v>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>76808</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>83700</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>97584</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>120326</v>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>78258</v>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>80054</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>79452</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>115942</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>84626</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>106590</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>120662</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>191500</v>
+        <v>213578</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>123342</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>96144</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>98858</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>173163</v>
+        <v>193032</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>106500</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>122124</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>10420</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>10420</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>10420</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>10420</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>11782</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>11782</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>11782</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>11782</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>13446</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>13446</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>13446</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>13446</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>14516</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>14516</v>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>14516</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>14516</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>15158</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>15158</v>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>15158</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>16384</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>16384</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>16384</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>92430</v>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>89070</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>59908</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>54678</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>74966</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>61664</v>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>52264</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>59534</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>72976</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>96920</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>53590</v>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>55440</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>52288</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>87174</v>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="D64" s="12" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>53408</v>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>74216</v>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>88896</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>129400</v>
+        <v>144900</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>94290</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>68016</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>66240</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="D70" s="12" t="n">
-        <v>103200</v>
+        <v>115600</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>73792</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>91520</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="D72" s="12" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>11484</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>13526</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="D74" s="12" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>14988</v>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>15644</v>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>15600</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>12306</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="D78" s="12" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>12762</v>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>12384</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="D80" s="12" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>11162</v>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>9960</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>11222</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>11168</v>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>12648</v>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>14252</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>16702</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>17858</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="E88" s="12" t="n">
         <v>16608</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>24600</v>
+        <v>26678</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>13894</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>12970</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>16234</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>29463</v>
+        <v>32082</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>16324</v>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>14220</v>
@@ -5173,7 +5173,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5225,7 +5225,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -5269,17 +5269,17 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="D6" s="13">
         <f>IF(C6=0,"",B6/C6-1)</f>
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>24116</v>
+        <v>28966</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -5293,17 +5293,17 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="D7" s="13">
         <f>IF(C7=0,"",B7/C7-1)</f>
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>36080</v>
+        <v>51480</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -5317,17 +5317,17 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="D8" s="13">
         <f>IF(C8=0,"",B8/C8-1)</f>
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>10925</v>
+        <v>13040</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -5341,17 +5341,17 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="D9" s="13">
         <f>IF(C9=0,"",B9/C9-1)</f>
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>71121</v>
+        <v>93486</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>
@@ -5364,7 +5364,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-07/growth-trades.xlsx
+++ b/media/exports/reports/2026-07/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>Workings!B37</f>
+        <f>Workings!B35</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B65</f>
+        <f>Workings!B63</f>
         <v/>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B41" s="9">
-        <f>Workings!B93</f>
+        <f>Workings!B91</f>
         <v/>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B53" s="9">
-        <f>Workings!B121</f>
+        <f>Workings!B119</f>
         <v/>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5173,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5225,7 +5225,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: July 2026 · Data status: Jun 2026 locked · Jul 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
